--- a/public/downloads/SchumannSelectivity2018.xlsx
+++ b/public/downloads/SchumannSelectivity2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CO</t>
@@ -656,10 +679,10 @@
         <v>22</v>
       </c>
       <c r="N3" s="5">
-        <v>214.6659383773804</v>
+        <v>214665.9383773804</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03071922415245855</v>
+        <v>30.71922415245855</v>
       </c>
       <c r="P3" s="5">
         <v>6988</v>
@@ -706,10 +729,10 @@
         <v>22</v>
       </c>
       <c r="N4" s="5">
-        <v>191.6859924793243</v>
+        <v>191685.9924793243</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04452636294525537</v>
+        <v>44.52636294525536</v>
       </c>
       <c r="P4" s="5">
         <v>4305</v>
@@ -756,10 +779,10 @@
         <v>22</v>
       </c>
       <c r="N5" s="5">
-        <v>429.527613401413</v>
+        <v>429527.613401413</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1771978603141142</v>
+        <v>177.1978603141143</v>
       </c>
       <c r="P5" s="5">
         <v>2424</v>
@@ -806,10 +829,10 @@
         <v>22</v>
       </c>
       <c r="N6" s="5">
-        <v>213.8143804073334</v>
+        <v>213814.3804073334</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08303471083779937</v>
+        <v>83.03471083779937</v>
       </c>
       <c r="P6" s="5">
         <v>2575</v>
@@ -856,10 +879,10 @@
         <v>22</v>
       </c>
       <c r="N7" s="5">
-        <v>757.510582447052</v>
+        <v>757510.582447052</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1527855148138467</v>
+        <v>152.7855148138467</v>
       </c>
       <c r="P7" s="5">
         <v>4958</v>
@@ -906,10 +929,10 @@
         <v>22</v>
       </c>
       <c r="N8" s="5">
-        <v>32.86777353286743</v>
+        <v>32867.77353286743</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01270988922384665</v>
+        <v>12.70988922384665</v>
       </c>
       <c r="P8" s="5">
         <v>2586</v>
@@ -956,10 +979,10 @@
         <v>22</v>
       </c>
       <c r="N9" s="5">
-        <v>77.44219923019409</v>
+        <v>77442.19923019409</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02992357002712291</v>
+        <v>29.92357002712291</v>
       </c>
       <c r="P9" s="5">
         <v>2588</v>
@@ -1006,10 +1029,10 @@
         <v>22</v>
       </c>
       <c r="N10" s="5">
-        <v>200.0535559654236</v>
+        <v>200053.5559654236</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08423307619596783</v>
+        <v>84.23307619596783</v>
       </c>
       <c r="P10" s="5">
         <v>2375</v>
@@ -1056,10 +1079,10 @@
         <v>22</v>
       </c>
       <c r="N11" s="5">
-        <v>337.8246567249298</v>
+        <v>337824.6567249298</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03949317941605446</v>
+        <v>39.49317941605446</v>
       </c>
       <c r="P11" s="5">
         <v>8554</v>
@@ -1106,10 +1129,10 @@
         <v>22</v>
       </c>
       <c r="N12" s="5">
-        <v>72.40095520019531</v>
+        <v>72400.95520019531</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01813196974710626</v>
+        <v>18.13196974710626</v>
       </c>
       <c r="P12" s="5">
         <v>3993</v>
@@ -1156,10 +1179,10 @@
         <v>22</v>
       </c>
       <c r="N13" s="5">
-        <v>883.5377502441406</v>
+        <v>883537.7502441406</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07489512166179034</v>
+        <v>74.89512166179034</v>
       </c>
       <c r="P13" s="5">
         <v>11797</v>
@@ -1206,10 +1229,10 @@
         <v>22</v>
       </c>
       <c r="N14" s="5">
-        <v>409.4243986606598</v>
+        <v>409424.3986606598</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2173165597986517</v>
+        <v>217.3165597986517</v>
       </c>
       <c r="P14" s="5">
         <v>1884</v>
@@ -1256,10 +1279,10 @@
         <v>22</v>
       </c>
       <c r="N15" s="5">
-        <v>498.8518328666687</v>
+        <v>498851.8328666687</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2334355792544074</v>
+        <v>233.4355792544075</v>
       </c>
       <c r="P15" s="5">
         <v>2137</v>
@@ -1306,10 +1329,10 @@
         <v>22</v>
       </c>
       <c r="N16" s="5">
-        <v>172.5039713382721</v>
+        <v>172503.9713382721</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09713061449227033</v>
+        <v>97.13061449227033</v>
       </c>
       <c r="P16" s="5">
         <v>1776</v>
@@ -1356,10 +1379,10 @@
         <v>22</v>
       </c>
       <c r="N17" s="5">
-        <v>423.159675359726</v>
+        <v>423159.675359726</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1057370503147741</v>
+        <v>105.7370503147741</v>
       </c>
       <c r="P17" s="5">
         <v>4002</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,37 +1494,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.259256784687441</v>
+        <v>1.081152304979002</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2307034355465057</v>
+        <v>0.6593199424560021</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2086451526637911</v>
+        <v>2.193384840825085</v>
       </c>
       <c r="E3" s="4">
-        <v>78.04634353741496</v>
+        <v>69.64285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>81.85123042505596</v>
+        <v>67.05327181208054</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -1496,36 +1551,54 @@
         <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1137511836443093</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.088897180220775</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5455687588116929</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1487120773869532</v>
+        <v>0.07723122456490654</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1487120773869532</v>
+        <v>0.07934961368115437</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1796749595536556</v>
+        <v>0.06040884393756684</v>
       </c>
       <c r="E4" s="4">
-        <v>83.14625850340137</v>
+        <v>85.1700680272109</v>
       </c>
       <c r="F4" s="4">
-        <v>88.02386278896344</v>
+        <v>86.20805369127471</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1539,9 +1612,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.02235700307190187</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06977889020760591</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06593541183801324</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,66 +1735,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>4.145067951487182</v>
+        <v>0.5187171625362543</v>
       </c>
       <c r="C3" s="4">
-        <v>0.197892356666749</v>
+        <v>0.5012563653597992</v>
       </c>
       <c r="D3" s="4">
-        <v>8.242013237284301</v>
+        <v>0.4513982154211613</v>
       </c>
       <c r="E3" s="4">
-        <v>67.72746598639466</v>
+        <v>78.42474489795919</v>
       </c>
       <c r="F3" s="4">
-        <v>70.54949664429625</v>
+        <v>84.30578859060402</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0009510430576478243</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5184794017718424</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5010368938849574</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3820012245804089</v>
+        <v>0.297828625460737</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1909582089624844</v>
+        <v>0.4172141118394688</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1433683866490938</v>
+        <v>0.4274630078942083</v>
       </c>
       <c r="E4" s="4">
-        <v>74.04761904761904</v>
+        <v>76.95578231292539</v>
       </c>
       <c r="F4" s="4">
-        <v>71.56040268456272</v>
+        <v>76.77665920954699</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1711,9 +1853,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.297828625460737</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4172141118394688</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1882,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1901,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1943,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,40 +1974,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.425417347215807</v>
+        <v>0.259256784687441</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7530996421251016</v>
+        <v>0.2307034355465057</v>
       </c>
       <c r="D3" s="4">
-        <v>3.47803775338325</v>
+        <v>0.2086451526637911</v>
       </c>
       <c r="E3" s="4">
-        <v>69.06037414965967</v>
+        <v>78.04634353741496</v>
       </c>
       <c r="F3" s="4">
-        <v>68.18442393736002</v>
+        <v>81.85123042505596</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
@@ -1842,25 +2033,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0003280851228064298</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2591747634067394</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2307332614667608</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.150920315587474</v>
+        <v>0.1487120773869532</v>
       </c>
       <c r="C4" s="4">
-        <v>0.150920315587474</v>
+        <v>0.1487120773869532</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1416118199968958</v>
+        <v>0.1796749595536556</v>
       </c>
       <c r="E4" s="4">
-        <v>76.60430839002267</v>
+        <v>83.14625850340137</v>
       </c>
       <c r="F4" s="4">
-        <v>82.00969425801644</v>
+        <v>88.02386278896344</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1883,9 +2092,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1487120773869532</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05626280120402804</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05626280120402804</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2123,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2142,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2184,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,25 +2215,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.289793887416454</v>
+        <v>4.145067951487182</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6343557584433108</v>
+        <v>0.197892356666749</v>
       </c>
       <c r="D3" s="4">
-        <v>5.499912658015818</v>
+        <v>8.242013237284301</v>
       </c>
       <c r="E3" s="4">
-        <v>65.2465986394557</v>
+        <v>67.72746598639466</v>
       </c>
       <c r="F3" s="4">
-        <v>62.77824384787472</v>
+        <v>70.54949664429625</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -2000,48 +2260,64 @@
         <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>3.188832202463327</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>4.143694491510547</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1693657095529427</v>
+        <v>0.3820012245804089</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1693657095529427</v>
+        <v>0.1909582089624844</v>
       </c>
       <c r="D4" s="4">
-        <v>0.0911439095169323</v>
+        <v>0.1433683866490938</v>
       </c>
       <c r="E4" s="4">
-        <v>84.38775510204076</v>
+        <v>74.04761904761904</v>
       </c>
       <c r="F4" s="4">
-        <v>84.99440715883617</v>
+        <v>71.56040268456272</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2055,9 +2331,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3820012245804089</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1909582089624844</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2360,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2379,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2421,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,40 +2452,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2996015609536442</v>
+        <v>1.425417347215807</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1751517716167449</v>
+        <v>0.7530996421251016</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2326243333061828</v>
+        <v>3.47803775338325</v>
       </c>
       <c r="E3" s="4">
-        <v>77.79336734693878</v>
+        <v>69.06037414965967</v>
       </c>
       <c r="F3" s="4">
-        <v>80.83892617449665</v>
+        <v>68.18442393736002</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
@@ -2186,34 +2511,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.10467928810947</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.425417347215807</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4099880700312729</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3746733992567899</v>
+        <v>0.150920315587474</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3971716307088419</v>
+        <v>0.150920315587474</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3920213708550569</v>
+        <v>0.1416118199968958</v>
       </c>
       <c r="E4" s="4">
-        <v>90.88435374149688</v>
+        <v>76.60430839002267</v>
       </c>
       <c r="F4" s="4">
-        <v>90.89858314690625</v>
+        <v>82.00969425801644</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2227,9 +2570,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.01136832145149479</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1471308751036423</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1471308751036423</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2601,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2620,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2662,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,34 +2693,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6257525464457225</v>
+        <v>1.289793887416454</v>
       </c>
       <c r="C3" s="4">
-        <v>0.540725895648263</v>
+        <v>0.6343557584433108</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5549084344816151</v>
+        <v>5.499912658015818</v>
       </c>
       <c r="E3" s="4">
-        <v>80.17006802721087</v>
+        <v>65.2465986394557</v>
       </c>
       <c r="F3" s="4">
-        <v>83.53607382550332</v>
+        <v>62.77824384787472</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2358,25 +2752,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6343557584433108</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.52453406840199</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2030699769992229</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2880672684042814</v>
+        <v>0.1693657095529427</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2880672684042814</v>
+        <v>0.1693657095529427</v>
       </c>
       <c r="D4" s="4">
-        <v>0.260959751479746</v>
+        <v>0.0911439095169323</v>
       </c>
       <c r="E4" s="4">
-        <v>80.71995464852603</v>
+        <v>84.38775510204076</v>
       </c>
       <c r="F4" s="4">
-        <v>86.15398956002993</v>
+        <v>84.99440715883617</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2399,9 +2811,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1608841092119115</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1157376731489722</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1157376731489722</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2842,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2861,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2903,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,25 +2934,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3164357240133776</v>
+        <v>0.2996015609536442</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1917122378929429</v>
+        <v>0.1751517716167449</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2511873761945261</v>
+        <v>0.2326243333061828</v>
       </c>
       <c r="E3" s="4">
-        <v>77.91666666666666</v>
+        <v>77.79336734693878</v>
       </c>
       <c r="F3" s="4">
-        <v>81.50517337807604</v>
+        <v>80.83892617449665</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -2530,25 +2993,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.144003390162072</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2813430244621674</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1847297211536846</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3999535569817778</v>
+        <v>0.3746733992567899</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4175210770989294</v>
+        <v>0.3971716307088419</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4143410056105259</v>
+        <v>0.3920213708550569</v>
       </c>
       <c r="E4" s="4">
-        <v>93.21428571428568</v>
+        <v>90.88435374149688</v>
       </c>
       <c r="F4" s="4">
-        <v>93.24384787472015</v>
+        <v>90.89858314690625</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2571,9 +3052,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.3971716307088419</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04361091010019572</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0253352143777725</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3083,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3091,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3102,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3144,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,75 +3175,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7729749305025062</v>
+        <v>0.6257525464457225</v>
       </c>
       <c r="C3" s="4">
-        <v>0.660753617253951</v>
+        <v>0.540725895648263</v>
       </c>
       <c r="D3" s="4">
-        <v>2.185781805574926</v>
+        <v>0.5549084344816151</v>
       </c>
       <c r="E3" s="4">
-        <v>69.45153061224489</v>
+        <v>80.17006802721087</v>
       </c>
       <c r="F3" s="4">
-        <v>73.55774608501119</v>
+        <v>83.53607382550332</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.540725895648263</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1685024927021305</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1027394977288258</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.055703434275623</v>
+        <v>0.2880672684042814</v>
       </c>
       <c r="C4" s="4">
-        <v>1.017588023096042</v>
+        <v>0.2880672684042814</v>
       </c>
       <c r="D4" s="4">
-        <v>1.136797818469015</v>
+        <v>0.260959751479746</v>
       </c>
       <c r="E4" s="4">
-        <v>77.64172335600929</v>
+        <v>80.71995464852603</v>
       </c>
       <c r="F4" s="4">
-        <v>76.31431767337672</v>
+        <v>86.15398956002993</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2743,9 +3293,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2880672684042814</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06432282584141698</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06432282584141698</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3324,1350 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3164357240133776</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1917122378929429</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2511873761945261</v>
+      </c>
+      <c r="E3" s="4">
+        <v>77.91666666666666</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.50517337807604</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1723157156396697</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2810458655056376</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1867818097322235</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3999535569817778</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4175210770989294</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4143410056105259</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.21428571428568</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.24384787472015</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.4175210770989294</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04895879861350679</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03766953419562617</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7729749305025062</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.660753617253951</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2.185781805574926</v>
+      </c>
+      <c r="E3" s="4">
+        <v>69.45153061224489</v>
+      </c>
+      <c r="F3" s="4">
+        <v>73.55774608501119</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2268389709315379</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7311302160323394</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3775166962536449</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.055703434275623</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.017588023096042</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.136797818469015</v>
+      </c>
+      <c r="E4" s="4">
+        <v>77.64172335600929</v>
+      </c>
+      <c r="F4" s="4">
+        <v>76.31431767337672</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.055703434275623</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.017588023096042</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="C3" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D3" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="E3" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.877037611504428</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2755863399809539</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.679383283251945</v>
+      </c>
+      <c r="K3" s="4">
+        <v>82.45207173778567</v>
+      </c>
+      <c r="L3" s="4">
+        <v>81.3702460850111</v>
+      </c>
+      <c r="M3" s="5">
+        <v>22</v>
+      </c>
+      <c r="N3" s="5">
+        <v>214665.9383773804</v>
+      </c>
+      <c r="O3" s="4">
+        <v>30.71922415245855</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6988</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>68.18181818181817</v>
+      </c>
+      <c r="C4" s="3">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2664329424540446</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2514288266336818</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2359812487644793</v>
+      </c>
+      <c r="K4" s="4">
+        <v>73.96876932591216</v>
+      </c>
+      <c r="L4" s="4">
+        <v>76.13077079520249</v>
+      </c>
+      <c r="M4" s="5">
+        <v>22</v>
+      </c>
+      <c r="N4" s="5">
+        <v>191685.9924793243</v>
+      </c>
+      <c r="O4" s="4">
+        <v>44.52636294525536</v>
+      </c>
+      <c r="P4" s="5">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C5" s="3">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.6069506003645676</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.5577875060383348</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.7170702228147702</v>
+      </c>
+      <c r="K5" s="4">
+        <v>80.04019789734078</v>
+      </c>
+      <c r="L5" s="4">
+        <v>81.42210697579704</v>
+      </c>
+      <c r="M5" s="5">
+        <v>22</v>
+      </c>
+      <c r="N5" s="5">
+        <v>429527.613401413</v>
+      </c>
+      <c r="O5" s="4">
+        <v>177.1978603141143</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1938201060157469</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2106207106251907</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3290531821464772</v>
+      </c>
+      <c r="K6" s="4">
+        <v>79.43568336425497</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.73388244864871</v>
+      </c>
+      <c r="M6" s="5">
+        <v>22</v>
+      </c>
+      <c r="N6" s="5">
+        <v>213814.3804073334</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.03471083779937</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="C7" s="3">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="D7" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="E7" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.334958054574683</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.8040820222682049</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.943236720038642</v>
+      </c>
+      <c r="K7" s="4">
+        <v>78.98886827458236</v>
+      </c>
+      <c r="L7" s="4">
+        <v>78.74161073825493</v>
+      </c>
+      <c r="M7" s="5">
+        <v>22</v>
+      </c>
+      <c r="N7" s="5">
+        <v>757510.582447052</v>
+      </c>
+      <c r="O7" s="4">
+        <v>152.7855148138467</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="C8" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="D8" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.8109558283990013</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3057520853248531</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.638706187812597</v>
+      </c>
+      <c r="K8" s="4">
+        <v>73.87755102040818</v>
+      </c>
+      <c r="L8" s="4">
+        <v>72.27730323367979</v>
+      </c>
+      <c r="M8" s="5">
+        <v>22</v>
+      </c>
+      <c r="N8" s="5">
+        <v>32867.77353286743</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.70988922384665</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="C9" s="3">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4583019173233591</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4853201222514283</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4449568900099603</v>
+      </c>
+      <c r="K9" s="4">
+        <v>78.02411873840489</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.25238966849614</v>
+      </c>
+      <c r="M9" s="5">
+        <v>22</v>
+      </c>
+      <c r="N9" s="5">
+        <v>77442.19923019409</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.92357002712291</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C10" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2038351373514544</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1691554519622669</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1674766759505991</v>
+      </c>
+      <c r="K10" s="4">
+        <v>79.43722943722892</v>
+      </c>
+      <c r="L10" s="4">
+        <v>83.53467561521326</v>
+      </c>
+      <c r="M10" s="5">
+        <v>22</v>
+      </c>
+      <c r="N10" s="5">
+        <v>200053.5559654236</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.23307619596783</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="C11" s="3">
+        <v>31.81818181818182</v>
+      </c>
+      <c r="D11" s="3">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="E11" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G11" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3.117778145984146</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1909582089624844</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5.450449491357682</v>
+      </c>
+      <c r="K11" s="4">
+        <v>69.45114409400129</v>
+      </c>
+      <c r="L11" s="4">
+        <v>70.82519829164086</v>
+      </c>
+      <c r="M11" s="5">
+        <v>22</v>
+      </c>
+      <c r="N11" s="5">
+        <v>337824.6567249298</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.49317941605446</v>
+      </c>
+      <c r="P11" s="5">
+        <v>8554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>50</v>
+      </c>
+      <c r="C12" s="3">
+        <v>31.81818181818182</v>
+      </c>
+      <c r="D12" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G12" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.076793763912489</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2666114182525653</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2.595758400166644</v>
+      </c>
+      <c r="K12" s="4">
+        <v>71.11781076066761</v>
+      </c>
+      <c r="L12" s="4">
+        <v>71.95495220663118</v>
+      </c>
+      <c r="M12" s="5">
+        <v>22</v>
+      </c>
+      <c r="N12" s="5">
+        <v>72400.95520019531</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.13196974710626</v>
+      </c>
+      <c r="P12" s="5">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="C13" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.140316869696621</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1594038250740976</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4.207670209067026</v>
+      </c>
+      <c r="K13" s="4">
+        <v>70.46691403834238</v>
+      </c>
+      <c r="L13" s="4">
+        <v>68.83719747813603</v>
+      </c>
+      <c r="M13" s="5">
+        <v>22</v>
+      </c>
+      <c r="N13" s="5">
+        <v>883537.7502441406</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.89512166179034</v>
+      </c>
+      <c r="P13" s="5">
+        <v>11797</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.2165069932725388</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1378489838666516</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1621631667359279</v>
+      </c>
+      <c r="K14" s="4">
+        <v>81.36363636363613</v>
+      </c>
+      <c r="L14" s="4">
+        <v>83.58246898515443</v>
+      </c>
+      <c r="M14" s="5">
+        <v>22</v>
+      </c>
+      <c r="N14" s="5">
+        <v>409424.3986606598</v>
+      </c>
+      <c r="O14" s="4">
+        <v>217.3165597986517</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="C15" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1400898562855723</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.09060791713280193</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.09261649323860571</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.32003710575141</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.25005084401221</v>
+      </c>
+      <c r="M15" s="5">
+        <v>22</v>
+      </c>
+      <c r="N15" s="5">
+        <v>498851.8328666687</v>
+      </c>
+      <c r="O15" s="4">
+        <v>233.4355792544075</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C16" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.2177493927168747</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1429252581038125</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1638251373424697</v>
+      </c>
+      <c r="K16" s="4">
+        <v>82.08874458874442</v>
+      </c>
+      <c r="L16" s="4">
+        <v>84.7066300589821</v>
+      </c>
+      <c r="M16" s="5">
+        <v>22</v>
+      </c>
+      <c r="N16" s="5">
+        <v>172503.9713382721</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.13061449227033</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="C17" s="3">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.819650184644144</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5908738052011105</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.872124720645819</v>
+      </c>
+      <c r="K17" s="4">
+        <v>71.68521954236246</v>
+      </c>
+      <c r="L17" s="4">
+        <v>74.30953833638303</v>
+      </c>
+      <c r="M17" s="5">
+        <v>22</v>
+      </c>
+      <c r="N17" s="5">
+        <v>423159.675359726</v>
+      </c>
+      <c r="O17" s="4">
+        <v>105.7370503147741</v>
+      </c>
+      <c r="P17" s="5">
+        <v>4002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,10 +4781,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3054,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3230,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3516,9 +5422,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>8</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>12</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6190,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6232,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6263,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>2.831287541667552</v>
@@ -3629,10 +6322,28 @@
       <c r="M3" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>2.248142620541217</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.558870176220164</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6726839502120855</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.06967327204603126</v>
@@ -3670,9 +6381,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.03803936575685938</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05881743892913021</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03732777384227499</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6412,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6431,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6473,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6504,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.7006183290791461</v>
@@ -3801,10 +6563,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.73271573046658</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2877990523136435</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2657777105629448</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2094566494951146</v>
@@ -3842,9 +6622,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2094566494951146</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05054445162400001</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6651,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6670,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6712,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6743,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6993603078258739</v>
@@ -3973,10 +6802,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4807113174963162</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8058185919890136</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8202338060414018</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.08477909886769623</v>
@@ -4014,9 +6861,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.02442942850495408</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07663595603271152</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07663595603271152</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6892,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6911,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6953,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6984,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2718417564944893</v>
@@ -4145,10 +7043,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.168879213603869</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2320543522163961</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2548044342493286</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.09186211614734895</v>
@@ -4186,9 +7102,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.001573792952518749</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09186211614734896</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.10457977392726</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7133,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7152,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7194,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7225,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.719440724641027</v>
@@ -4317,10 +7284,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.222486659508845</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.826562761221807</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.389134411332595</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1688964694013698</v>
@@ -4358,9 +7343,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1688964694013698</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.02401217018235068</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.02401217018235068</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7374,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.081152304979002</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6593199424560021</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.193384840825085</v>
-      </c>
-      <c r="E3" s="4">
-        <v>69.64285714285714</v>
-      </c>
-      <c r="F3" s="4">
-        <v>67.05327181208054</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5">
-        <v>9</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.07723122456490654</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.07934961368115437</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.06040884393756684</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.1700680272109</v>
-      </c>
-      <c r="F4" s="4">
-        <v>86.20805369127471</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5187171625362543</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5012563653597992</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4513982154211613</v>
-      </c>
-      <c r="E3" s="4">
-        <v>78.42474489795919</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.30578859060402</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.297828625460737</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4172141118394688</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4274630078942083</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.95578231292539</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.77665920954699</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SchumannSelectivity2018.xlsx
+++ b/public/downloads/SchumannSelectivity2018.xlsx
@@ -1554,16 +1554,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1137511836443093</v>
+        <v>-0.6157747230114509</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>1.088897180220775</v>
+        <v>1.193919416550658</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5455687588116929</v>
+        <v>0.1503631656015315</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02235700307190187</v>
+        <v>-0.04747377081316173</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06977889020760591</v>
+        <v>0.06170964312500387</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06593541183801324</v>
+        <v>0.05122896179063881</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0009510430576478243</v>
+        <v>-0.1384908521914843</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5184794017718424</v>
+        <v>0.4959413878595551</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5010368938849574</v>
+        <v>0.4838777851570529</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -2034,16 +2034,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0003280851228064298</v>
+        <v>0.05465036177534732</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2591747634067394</v>
+        <v>0.2729193751312778</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2307332614667608</v>
+        <v>0.2257352208396559</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1487120773869532</v>
+        <v>-0.1572030053583514</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -2275,20 +2275,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>3.188832202463327</v>
+        <v>-0.08345251786554686</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>4.143694491510547</v>
-      </c>
-      <c r="Q3" s="4"/>
+        <v>4.178890425558968</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1489980910822698</v>
+      </c>
       <c r="R3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2512,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.10467928810947</v>
+        <v>-0.436844554797793</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>1.425417347215807</v>
+        <v>1.465042451050842</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4099880700312729</v>
+        <v>0.159899406692075</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2571,16 +2573,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01136832145149479</v>
+        <v>0.04196071396692186</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1471308751036423</v>
+        <v>0.1394232942935677</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1471308751036423</v>
+        <v>0.1394232942935677</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2753,13 +2755,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6343557584433108</v>
+        <v>-0.6924088397207734</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>1.52453406840199</v>
+        <v>1.560817244200404</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2030699769992229</v>
@@ -2812,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1608841092119115</v>
+        <v>0.2027410554074219</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1157376731489722</v>
+        <v>0.1094585320460104</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1157376731489722</v>
+        <v>0.1094585320460104</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2994,16 +2996,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.144003390162072</v>
+        <v>-0.04738564653245492</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2813430244621674</v>
+        <v>0.2844536565259986</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1847297211536846</v>
+        <v>0.1707497812240357</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3053,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3971716307088419</v>
+        <v>-0.3948076971576701</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04361091010019572</v>
+        <v>0.04282293224980513</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0253352143777725</v>
+        <v>0.02486242766753815</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3235,16 +3237,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.540725895648263</v>
+        <v>-0.5485429531723169</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1685024927021305</v>
+        <v>0.166548228321117</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1027394977288258</v>
+        <v>0.1021381856115909</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3294,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2880672684042814</v>
+        <v>0.2738579173568813</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
@@ -3476,16 +3478,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1723157156396697</v>
+        <v>-0.07725774556032394</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2810458655056376</v>
+        <v>0.2814575745514299</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1867818097322235</v>
+        <v>0.1708272871304539</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3535,16 +3537,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4175210770989294</v>
+        <v>-0.416388811412337</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04895879861350679</v>
+        <v>0.048581376717976</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03766953419562617</v>
+        <v>0.0374430810583077</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3717,16 +3719,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2268389709315379</v>
+        <v>-0.5479968072831747</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7311302160323394</v>
+        <v>0.7044525432132434</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3775166962536449</v>
+        <v>0.2438718915275436</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -3902,13 +3904,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>36.36363636363637</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3">
         <v>18.18181818181818</v>
       </c>
       <c r="D3" s="3">
-        <v>45.45454545454545</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="E3" s="3">
         <v>9.090909090909092</v>
@@ -3917,16 +3919,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>36.36363636363637</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="H3" s="4">
         <v>1.877037611504428</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2755863399809539</v>
+        <v>0.8155503071050142</v>
       </c>
       <c r="J3" s="4">
-        <v>3.679383283251945</v>
+        <v>3.798332478147327</v>
       </c>
       <c r="K3" s="4">
         <v>82.45207173778567</v>
@@ -3970,13 +3972,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2664329424540446</v>
+        <v>0.2653041872064611</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2514288266336818</v>
+        <v>0.2497733189372258</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2359812487644793</v>
+        <v>0.2427973515500157</v>
       </c>
       <c r="K4" s="4">
         <v>73.96876932591216</v>
@@ -4002,13 +4004,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>77.27272727272727</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="C5" s="3">
         <v>22.72727272727273</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -4017,16 +4019,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="H5" s="4">
-        <v>0.6069506003645676</v>
+        <v>0.546842472217791</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5577875060383348</v>
+        <v>0.4457141452612779</v>
       </c>
       <c r="J5" s="4">
-        <v>0.7170702228147702</v>
+        <v>0.7173832164772809</v>
       </c>
       <c r="K5" s="4">
         <v>80.04019789734078</v>
@@ -4070,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1938201060157469</v>
+        <v>0.1961827054031617</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2106207106251907</v>
+        <v>0.2056030640916338</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3290531821464772</v>
+        <v>0.3152962446670529</v>
       </c>
       <c r="K6" s="4">
         <v>79.43568336425497</v>
@@ -4102,13 +4104,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>63.63636363636363</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="C7" s="3">
         <v>22.72727272727273</v>
       </c>
       <c r="D7" s="3">
-        <v>13.63636363636363</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="E7" s="3">
         <v>9.090909090909092</v>
@@ -4117,16 +4119,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>4.545454545454546</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="H7" s="4">
-        <v>1.334958054574683</v>
+        <v>1.281311668205259</v>
       </c>
       <c r="I7" s="4">
-        <v>0.8040820222682049</v>
+        <v>0.1331479078220716</v>
       </c>
       <c r="J7" s="4">
-        <v>1.943236720038642</v>
+        <v>2.199486380032271</v>
       </c>
       <c r="K7" s="4">
         <v>78.98886827458236</v>
@@ -4170,13 +4172,13 @@
         <v>4.545454545454546</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8109558283990013</v>
+        <v>0.8851349328891162</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3057520853248531</v>
+        <v>0.1007960636960852</v>
       </c>
       <c r="J8" s="4">
-        <v>1.638706187812597</v>
+        <v>1.80322673256465</v>
       </c>
       <c r="K8" s="4">
         <v>73.87755102040818</v>
@@ -4220,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4583019173233591</v>
+        <v>0.4419106344780592</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4853201222514283</v>
+        <v>0.4713783464100059</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4449568900099603</v>
+        <v>0.4797915399246575</v>
       </c>
       <c r="K9" s="4">
         <v>78.02411873840489</v>
@@ -4270,13 +4272,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2038351373514544</v>
+        <v>0.2138312186056642</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1691554519622669</v>
+        <v>0.1659214256741402</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1674766759505991</v>
+        <v>0.167761560017172</v>
       </c>
       <c r="K10" s="4">
         <v>79.43722943722892</v>
@@ -4302,13 +4304,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>13.63636363636363</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="C11" s="3">
         <v>31.81818181818182</v>
       </c>
       <c r="D11" s="3">
-        <v>54.54545454545454</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="E11" s="3">
         <v>13.63636363636363</v>
@@ -4317,16 +4319,16 @@
         <v>4.545454545454546</v>
       </c>
       <c r="G11" s="3">
-        <v>36.36363636363637</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="H11" s="4">
-        <v>3.117778145984146</v>
+        <v>3.143375188928452</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1909582089624844</v>
+        <v>0.1629847970423413</v>
       </c>
       <c r="J11" s="4">
-        <v>5.450449491357682</v>
+        <v>6.060160169008797</v>
       </c>
       <c r="K11" s="4">
         <v>69.45114409400129</v>
@@ -4370,13 +4372,13 @@
         <v>4.545454545454546</v>
       </c>
       <c r="H12" s="4">
-        <v>1.076793763912489</v>
+        <v>1.103509953753403</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2666114182525653</v>
+        <v>0.148730618111071</v>
       </c>
       <c r="J12" s="4">
-        <v>2.595758400166644</v>
+        <v>2.706571620772209</v>
       </c>
       <c r="K12" s="4">
         <v>71.11781076066761</v>
@@ -4420,13 +4422,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>1.140316869696621</v>
+        <v>1.164992140885569</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1594038250740976</v>
+        <v>0.1562642545226167</v>
       </c>
       <c r="J13" s="4">
-        <v>4.207670209067026</v>
+        <v>4.241668327137784</v>
       </c>
       <c r="K13" s="4">
         <v>70.46691403834238</v>
@@ -4470,13 +4472,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.2165069932725388</v>
+        <v>0.2185543680870367</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1378489838666516</v>
+        <v>0.12784173606036</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1621631667359279</v>
+        <v>0.1648568221671664</v>
       </c>
       <c r="K14" s="4">
         <v>81.36363636363613</v>
@@ -4520,13 +4522,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1400898562855723</v>
+        <v>0.1386685730993807</v>
       </c>
       <c r="I15" s="4">
-        <v>0.09060791713280193</v>
+        <v>0.09019649305258859</v>
       </c>
       <c r="J15" s="4">
-        <v>0.09261649323860571</v>
+        <v>0.09083034894398125</v>
       </c>
       <c r="K15" s="4">
         <v>80.32003710575141</v>
@@ -4570,13 +4572,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2177493927168747</v>
+        <v>0.2179458842332152</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1429252581038125</v>
+        <v>0.131596638285705</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1638251373424697</v>
+        <v>0.1681095641939644</v>
       </c>
       <c r="K16" s="4">
         <v>82.08874458874442</v>
@@ -4620,13 +4622,13 @@
         <v>4.545454545454546</v>
       </c>
       <c r="H17" s="4">
-        <v>0.819650184644144</v>
+        <v>0.8002482407757104</v>
       </c>
       <c r="I17" s="4">
-        <v>0.5908738052011105</v>
+        <v>0.5017772687170431</v>
       </c>
       <c r="J17" s="4">
-        <v>1.872124720645819</v>
+        <v>1.868473116004547</v>
       </c>
       <c r="K17" s="4">
         <v>71.68521954236246</v>
@@ -5509,13 +5511,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5">
         <v>4</v>
       </c>
       <c r="D3" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>2</v>
@@ -5524,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H3" s="5">
         <v>2</v>
@@ -5597,13 +5599,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="5">
         <v>5</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -5612,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -5685,13 +5687,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5">
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -5700,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5">
         <v>2</v>
@@ -5861,13 +5863,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5">
         <v>7</v>
       </c>
       <c r="D11" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5">
         <v>3</v>
@@ -5876,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H11" s="5">
         <v>3</v>
@@ -6323,7 +6325,7 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>2.248142620541217</v>
+        <v>1.167447634364004</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
@@ -6332,13 +6334,13 @@
         <v>2.558870176220164</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6726839502120855</v>
+        <v>1.468300432956386</v>
       </c>
       <c r="R3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S3" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6382,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03803936575685938</v>
+        <v>-0.06342745455139065</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -6391,7 +6393,7 @@
         <v>0.05881743892913021</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03732777384227499</v>
+        <v>0.03225015608336874</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -6564,16 +6566,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.73271573046658</v>
+        <v>-0.7717203720120215</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2877990523136435</v>
+        <v>0.286247013848216</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2657777105629448</v>
+        <v>0.264003952316742</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -6803,22 +6805,22 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4807113174963162</v>
+        <v>0.1980992053474069</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8058185919890136</v>
+        <v>0.7241227084942996</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8202338060414018</v>
+        <v>0.6686855271297839</v>
       </c>
       <c r="R3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6862,16 +6864,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02442942850495408</v>
+        <v>-0.033483244027569</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07663595603271152</v>
+        <v>0.07409517548043486</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07663595603271152</v>
+        <v>0.07409517548043486</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -7044,16 +7046,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.168879213603869</v>
+        <v>-0.127650143622832</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2320543522163961</v>
+        <v>0.2353029263740914</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2548044342493286</v>
+        <v>0.2522643547960828</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -7103,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.001573792952518749</v>
+        <v>0.05324524467899999</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -7112,7 +7114,7 @@
         <v>0.09186211614734896</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.10457977392726</v>
+        <v>0.09361596640095624</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7285,22 +7287,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>1.222486659508845</v>
+        <v>-0.2690789727355469</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>1.826562761221807</v>
+        <v>1.75307559623297</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.389134411332595</v>
+        <v>0.2273250915569678</v>
       </c>
       <c r="R3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7344,16 +7346,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1688964694013698</v>
+        <v>-0.175213854599875</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.02401217018235068</v>
+        <v>0.02327452679802604</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.02401217018235068</v>
+        <v>0.02327452679802604</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
